--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t xml:space="preserve">Строки</t>
   </si>
@@ -43,7 +43,13 @@
     <t xml:space="preserve">max_sqe_len</t>
   </si>
   <si>
+    <t xml:space="preserve">train loss</t>
+  </si>
+  <si>
     <t xml:space="preserve">emb_size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valid loss</t>
   </si>
   <si>
     <t xml:space="preserve">W_k</t>
@@ -114,7 +120,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +150,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i val="true"/>
@@ -266,72 +278,80 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -587,319 +607,348 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="D1:K24"/>
+  <dimension ref="D1:O32"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="5.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="5.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="G2" s="3" t="n">
+      <c r="F2" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>512000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="F3" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>768000</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="6" t="n">
         <v>2000</v>
       </c>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="6" t="n">
         <v>3000</v>
       </c>
+      <c r="N4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>4.07247924804688</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="8"/>
-      <c r="J5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>256</v>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10"/>
+      <c r="J5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>256</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>4.47794103622437</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>16384</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>16384</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="F6" s="3" t="n">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G8" s="11" t="n">
         <v>16384</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>16384</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K7" s="5" t="n">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="11" t="n">
+        <v>49152</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>16384</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="9" t="n">
-        <v>49152</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="2" t="e">
+      <c r="F10" s="3" t="e">
         <f aca="false">#ERR520!</f>
         <v>#N/A</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="11" t="n">
         <v>393216</v>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>16</v>
+      <c r="H10" s="14" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="3" t="n">
+      <c r="D11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>512</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="G11" s="9" t="n">
+      <c r="F11" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="G11" s="11" t="n">
         <v>131072</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="9" t="n">
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="11" t="n">
         <v>524288</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>18</v>
+      <c r="H12" s="14" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="13"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="F15" s="3" t="n">
+      <c r="D15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="F15" s="4" t="n">
         <v>1024</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="11" t="n">
         <v>262144</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="3" t="n">
+      <c r="D16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>1024</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="G16" s="9" t="n">
+      <c r="F16" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="G16" s="11" t="n">
         <v>262144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="11" t="n">
         <v>524288</v>
       </c>
-      <c r="H17" s="12" t="s">
-        <v>21</v>
+      <c r="H17" s="14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="3" t="n">
+      <c r="D18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="G18" s="9" t="n">
+      <c r="F18" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="G18" s="11" t="n">
         <v>512</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="3" t="n">
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="G19" s="9" t="n">
+      <c r="F19" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="G19" s="11" t="n">
         <v>512</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="11" t="n">
         <v>1049600</v>
       </c>
-      <c r="H20" s="12" t="s">
-        <v>24</v>
+      <c r="H20" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3" t="n">
+      <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F21" s="2" t="e">
+      <c r="F21" s="3" t="e">
         <f aca="false">#ERR520!</f>
         <v>#N/A</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="11" t="n">
         <v>9446400</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>26</v>
+      <c r="H21" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="F22" s="3" t="n">
+      <c r="D22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="F22" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="11" t="n">
         <v>512000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="16" t="n">
+      <c r="G24" s="18" t="n">
         <v>11238400</v>
       </c>
-      <c r="H24" s="16" t="s">
-        <v>27</v>
-      </c>
+      <c r="H24" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D30" s="0"/>
+      <c r="E30" s="0"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D31" s="0"/>
+      <c r="E31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D32" s="0"/>
+      <c r="E32" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
